--- a/examples/excel/charts/charts-extended.xlsx
+++ b/examples/excel/charts/charts-extended.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Waterfall &amp; Funnel" sheetId="2" r:id="R38a288d9d7824b0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Treemap &amp; Sunburst" sheetId="3" r:id="R63f0dfea0f6b4c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Histogram &amp; BoxWhisker" sheetId="4" r:id="R01a3eea11b524030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Pareto" sheetId="5" r:id="R26db7af80c6b4d15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Chart Meta" sheetId="6" r:id="R7c09be016ba74e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Waterfall &amp; Funnel" sheetId="2" r:id="R63c598e5223543d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Treemap &amp; Sunburst" sheetId="3" r:id="R347d612b74404712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Histogram &amp; BoxWhisker" sheetId="4" r:id="R5e21e1b45bfd4a58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Pareto" sheetId="5" r:id="Ree8072634370494d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-Chart Meta" sheetId="6" r:id="R6b97201feb1943f3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -881,9 +881,6 @@
             <c:v>A</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4472C4"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
               <a:solidFill>
                 <a:srgbClr val="4472C4"/>
@@ -933,9 +930,6 @@
             <c:v>B</c:v>
           </c:tx>
           <c:spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="ED7D31"/>
-            </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="25400">
               <a:solidFill>
                 <a:srgbClr val="ED7D31"/>
@@ -1305,7 +1299,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R16bb2156888d4e3e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3794953ef8b74c4a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1335,7 +1329,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea493661dee04a3f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R28016902fdf145b1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1365,7 +1359,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re557b41a8eda4c51"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rb5399d2928d6470c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1395,7 +1389,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R60af46fa167241d9"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ra4ab2bc35bbb4a67"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1430,7 +1424,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4908ebaf4b3646bf"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R9c2be4332db046cb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1460,7 +1454,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ra6022177007d4bdf"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R5308a0dd1c714ccc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1490,7 +1484,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rdd434730e2a84ca8"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R2e9ce7e1c6ee4bf2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1520,7 +1514,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R4ad3be7fead24a2b"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R74c20ae46d1840ed"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1555,7 +1549,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rcf5cc70d93c84132"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R6e092409ba0b4912"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1585,7 +1579,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R1ce19ec7a17543af"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R9d6e755b90524332"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1615,7 +1609,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rede6a523f2a841e7"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R20f6917fc95f4df6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1645,7 +1639,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R0a3499650b6047b1"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R859d7e272a9f4c2a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1675,7 +1669,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Ree19684747f344e9"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R9eb14b95594b4356"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1705,7 +1699,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="R77b36aecfff24c35"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rf0f9dd56cb744d53"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1740,7 +1734,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rfa0cd2b208c445b8"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Re35c712410c543a3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1770,7 +1764,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rae3545e4d1bd4b6a"/>
+          <cx:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" r:id="Rf8e7b69ab153485e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1805,7 +1799,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38ae65264bec4d0e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R23b797c0fe2e496c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1835,7 +1829,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9018d21e3b9b4c63"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra080496de599483d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1865,7 +1859,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rae4ee40434be4ea2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8bafc55327c245a4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1895,7 +1889,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rab5a065b748c4abb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R664903f8c05b4862"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1954,7 +1948,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="funnel" uniqueId="{D07791CF-9675-44C3-BA6D-61E699815084}">
+        <cx:series layoutId="funnel" uniqueId="{FA5CACB5-48C4-4B7F-8AC1-7B851C5E8157}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Waterfall &amp; Funnel!$B$1</cx:f>
@@ -2020,7 +2014,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{F6720569-3805-41E7-958D-4DEB524C9CCD}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{6E804FAD-2019-48D4-9420-E90EA405EB82}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
@@ -2150,7 +2144,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{107B3AB6-AE94-4CEE-A245-7DE59D272FC7}">
+        <cx:series layoutId="boxWhisker" uniqueId="{4137AA20-7752-4CC3-A210-0FBFD8801512}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
@@ -2163,7 +2157,7 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{BFCD8264-729C-4BAC-A38C-8B76DF57C87A}">
+        <cx:series layoutId="boxWhisker" uniqueId="{97F6DDB2-0DC0-4555-8005-435BC3220F1C}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$C$1</cx:f>
@@ -2324,7 +2318,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{C59E155E-85CE-4657-A740-851E4D2B1C5C}">
+        <cx:series layoutId="boxWhisker" uniqueId="{E25834D3-AA9E-4C0E-81FA-81912E2052FC}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
@@ -2337,7 +2331,7 @@
             <cx:statistics quartileMethod="inclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{BAA4CC7F-620C-4A76-BE2F-50FAA74A58CF}">
+        <cx:series layoutId="boxWhisker" uniqueId="{7A5F7598-3469-4CD0-8761-726DD3F2EFA4}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$C$1</cx:f>
@@ -2350,7 +2344,7 @@
             <cx:statistics quartileMethod="inclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{8C16DDC6-0537-4B29-A581-BF3EAB519CA2}">
+        <cx:series layoutId="boxWhisker" uniqueId="{11218E64-AD3C-4CB8-8490-939AC840FE6E}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$D$1</cx:f>
@@ -2423,7 +2417,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{4E05D8C4-ADE0-4042-8E3D-C74F31311E67}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{FF46DC9C-BB40-42B4-9479-B6DDD12FA03C}">
           <cx:tx>
             <cx:txData>
               <cx:f>4-Pareto!$B$1</cx:f>
@@ -2511,7 +2505,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{F006F790-1971-4A49-AFE2-890E9402FDA9}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{91025666-7C28-4B25-A25F-A631359C0BEE}">
           <cx:tx>
             <cx:txData>
               <cx:f>4-Pareto!$B$1</cx:f>
@@ -2589,7 +2583,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="funnel" uniqueId="{1AA830F7-81E5-40B7-A165-FB7212C112D7}">
+        <cx:series layoutId="funnel" uniqueId="{F346C16F-CD61-4313-A996-AB409445DE3A}">
           <cx:tx>
             <cx:txData>
               <cx:f>1-Waterfall &amp; Funnel!$B$1</cx:f>
@@ -2659,7 +2653,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="treemap" uniqueId="{37E71C1B-209D-48AA-9D38-475E6E0ABBB1}">
+        <cx:series layoutId="treemap" uniqueId="{9259F0EA-C15E-4D27-B171-94A1BF73F8C4}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Treemap &amp; Sunburst!$B$1</cx:f>
@@ -2730,7 +2724,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="treemap" uniqueId="{7971E7B7-30D2-4A6C-A3E1-8E0AF3EA4BC0}">
+        <cx:series layoutId="treemap" uniqueId="{F7F1EC8E-DCD2-4851-BDFF-D1C5059CC018}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Treemap &amp; Sunburst!$B$1</cx:f>
@@ -2800,7 +2794,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="treemap" uniqueId="{E5A2032F-84C8-4D82-A28F-4357ABEA38FA}">
+        <cx:series layoutId="treemap" uniqueId="{BD55F04D-490C-4EB1-9076-99F6BE13204C}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Treemap &amp; Sunburst!$B$1</cx:f>
@@ -2871,7 +2865,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="sunburst" uniqueId="{74C0273F-B5A3-4723-B292-209BD7B96C98}">
+        <cx:series layoutId="sunburst" uniqueId="{C02B2169-BE11-486C-AE58-7FBEA57B6555}">
           <cx:tx>
             <cx:txData>
               <cx:f>2-Treemap &amp; Sunburst!$B$1</cx:f>
@@ -2962,7 +2956,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{F19BFD0F-4032-402A-B806-12474F77B534}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{43DC3C5C-133A-4106-A9D0-678F431550C4}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
@@ -3041,7 +3035,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{46D8CAF8-B41F-4A69-AE39-0DB40E017326}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{78873BA8-6B84-416C-BA5D-58047D9859D3}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
@@ -3122,7 +3116,7 @@
     </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="clusteredColumn" uniqueId="{FF9094B6-A272-40A7-B108-639FDF938326}">
+        <cx:series layoutId="clusteredColumn" uniqueId="{84A56BC5-F822-4262-BEE9-D9AFCBF3C067}">
           <cx:tx>
             <cx:txData>
               <cx:f>3-Histogram &amp; BoxWhisker!$B$1</cx:f>
@@ -10290,6 +10284,115 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData>
@@ -10347,7 +10450,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a1b59d1d47b42f5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a61b65523914828"/>
 </x:worksheet>
 </file>
 
@@ -10440,7 +10543,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R871e20c96f1347f4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90dead01dc3447c9"/>
 </x:worksheet>
 </file>
 
@@ -10720,7 +10823,7 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rec4fa5fd03fe4f0d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f3e884a67d045e1"/>
 </x:worksheet>
 </file>
 
@@ -10813,13 +10916,13 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaf173fdad76458a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcec84e9ce5d54164"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0015d122a6be4c4d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d6b1c94cfe24733"/>
 </x:worksheet>
 </file>